--- a/artfynd/A 23100-2026 artfynd.xlsx
+++ b/artfynd/A 23100-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -775,48 +775,48 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>68154008</v>
+        <v>134636358</v>
       </c>
       <c r="B3" t="n">
-        <v>75428</v>
+        <v>92647</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6426</v>
+        <v>1339</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Hösterum, Fredrikslund, Ög</t>
+          <t>Fredrikslund, Ög</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>590312</v>
+        <v>590311</v>
       </c>
       <c r="R3" t="n">
-        <v>6468530</v>
+        <v>6468514</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -840,12 +840,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2017-10-26</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2017-10-26</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -860,15 +860,597 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>68154008</v>
+      </c>
+      <c r="B4" t="n">
+        <v>75428</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>6426</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Kattfotslav</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Felipes leucopellaeus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Hösterum, Fredrikslund, Ög</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>590312</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6468530</v>
+      </c>
+      <c r="S4" t="n">
+        <v>25</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Söderköping</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Mogata</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2017-10-26</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2017-10-26</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
           <t>Mikael Hagström</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
+      <c r="AX4" t="inlineStr">
         <is>
           <t>Mikael Hagström</t>
         </is>
       </c>
-      <c r="AY3" t="inlineStr"/>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>134636347</v>
+      </c>
+      <c r="B5" t="n">
+        <v>75468</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>6426</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Kattfotslav</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Felipes leucopellaeus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Fredrikslund, Ög</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>590317</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6468523</v>
+      </c>
+      <c r="S5" t="n">
+        <v>15</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Söderköping</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Mogata</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>134636342</v>
+      </c>
+      <c r="B6" t="n">
+        <v>75354</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>6427</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Glansfläck</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Diarthonis spadicea</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Leight.) Frisch &amp; al.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Fredrikslund, Ög</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>590318</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6468540</v>
+      </c>
+      <c r="S6" t="n">
+        <v>15</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Söderköping</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Mogata</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>134636351</v>
+      </c>
+      <c r="B7" t="n">
+        <v>75354</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>6427</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Glansfläck</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Diarthonis spadicea</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Leight.) Frisch &amp; al.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Fredrikslund, Ög</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>590311</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6468520</v>
+      </c>
+      <c r="S7" t="n">
+        <v>15</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Söderköping</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Mogata</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>134636345</v>
+      </c>
+      <c r="B8" t="n">
+        <v>81031</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>6444</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Skriftlav</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Graphis scripta</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Fredrikslund, Ög</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>590330</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6468534</v>
+      </c>
+      <c r="S8" t="n">
+        <v>15</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Söderköping</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Mogata</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>134636350</v>
+      </c>
+      <c r="B9" t="n">
+        <v>81031</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>6444</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Skriftlav</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Graphis scripta</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Fredrikslund, Ög</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>590325</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6468516</v>
+      </c>
+      <c r="S9" t="n">
+        <v>15</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Söderköping</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Mogata</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 23100-2026 artfynd.xlsx
+++ b/artfynd/A 23100-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AZ9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -772,6 +777,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/68154007</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -869,6 +879,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134636358</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -966,6 +981,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/68154008</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1063,6 +1083,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134636347</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1160,6 +1185,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134636342</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1257,6 +1287,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134636351</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1354,6 +1389,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134636345</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1451,8 +1491,23 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134636350</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>